--- a/public/templates/early-attendance-empty.xlsx
+++ b/public/templates/early-attendance-empty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dodt\Desktop\cham-cong\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC31262-EFC2-452E-BDB8-476529C68388}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04865BE7-B847-4545-A5EF-A11E82F30055}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,17 +93,20 @@
       <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
